--- a/HIstoricoDoMeuExperimento.xlsx
+++ b/HIstoricoDoMeuExperimento.xlsx
@@ -401,7 +401,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Model Name and Version - Agent Name - Skills and Agents</v>
+        <v>Gemini 3.1 Pro - VSCode Copilot</v>
       </c>
     </row>
     <row r="2">
